--- a/Resources/YardLayout.xlsx
+++ b/Resources/YardLayout.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grady Seaward\Documents\GitHub\Material Web App\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FA39AB-1AB1-4497-8976-83EDDA08E4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1D9C24-93BF-4112-8ECB-76E3D5BB19A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E0D74A12-1445-45BF-ABD1-708AC5091B34}"/>
+    <workbookView xWindow="-45120" yWindow="-5415" windowWidth="29040" windowHeight="15720" xr2:uid="{E0D74A12-1445-45BF-ABD1-708AC5091B34}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -411,20 +411,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -434,18 +446,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -804,19 +804,19 @@
       <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="10"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="C2" s="11" t="str">
+      <c r="C2" s="8" t="str">
         <f>_xlfn.TEXTJOIN("-", TRUE, _xlfn.UNIQUE(D2:H2))</f>
         <v>King</v>
       </c>
@@ -833,7 +833,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="11" t="str">
+      <c r="C3" s="8" t="str">
         <f t="shared" ref="C3:C65" si="0">_xlfn.TEXTJOIN("-", TRUE, _xlfn.UNIQUE(D3:H3))</f>
         <v>King-WA</v>
       </c>
@@ -852,7 +852,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="11" t="str">
+      <c r="C4" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WA-1</v>
       </c>
@@ -873,7 +873,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="11" t="str">
+      <c r="C5" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WA-2</v>
       </c>
@@ -894,7 +894,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="11" t="str">
+      <c r="C6" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WA-3</v>
       </c>
@@ -915,7 +915,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="11" t="str">
+      <c r="C7" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WA-4</v>
       </c>
@@ -936,7 +936,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="11" t="str">
+      <c r="C8" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WB</v>
       </c>
@@ -955,7 +955,7 @@
         <v>19</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="11" t="str">
+      <c r="C9" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WB-1</v>
       </c>
@@ -976,7 +976,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="11" t="str">
+      <c r="C10" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WB-2</v>
       </c>
@@ -997,7 +997,7 @@
         <v>21</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="11" t="str">
+      <c r="C11" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WB-3</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="11" t="str">
+      <c r="C12" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WB-4</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="11" t="str">
+      <c r="C13" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WC</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="11" t="str">
+      <c r="C14" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WD</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="11" t="str">
+      <c r="C15" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WD-1</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="11" t="str">
+      <c r="C16" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WD-2</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>21</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="11" t="str">
+      <c r="C17" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WD-3</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>22</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="11" t="str">
+      <c r="C18" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WD-4</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>26</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="11" t="str">
+      <c r="C19" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WE</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="11" t="str">
+      <c r="C20" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WE-1</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="4"/>
-      <c r="C21" s="11" t="str">
+      <c r="C21" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WE-2</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="11" t="str">
+      <c r="C22" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WE-3</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="11" t="str">
+      <c r="C23" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WE-4</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="4"/>
-      <c r="C24" s="11" t="str">
+      <c r="C24" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WM</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>28</v>
       </c>
       <c r="B25" s="4"/>
-      <c r="C25" s="11" t="str">
+      <c r="C25" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WO</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>19</v>
       </c>
       <c r="B26" s="4"/>
-      <c r="C26" s="11" t="str">
+      <c r="C26" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WO-1</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="4"/>
-      <c r="C27" s="11" t="str">
+      <c r="C27" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-WO-2</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="4"/>
-      <c r="C28" s="11" t="str">
+      <c r="C28" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-Y</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="4"/>
-      <c r="C29" s="11" t="str">
+      <c r="C29" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-Y-1</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>31</v>
       </c>
       <c r="B30" s="4"/>
-      <c r="C30" s="11" t="str">
+      <c r="C30" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-Y-2</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>32</v>
       </c>
       <c r="B31" s="4"/>
-      <c r="C31" s="11" t="str">
+      <c r="C31" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-Y-3</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>33</v>
       </c>
       <c r="B32" s="4"/>
-      <c r="C32" s="11" t="str">
+      <c r="C32" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-Y-4</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>34</v>
       </c>
       <c r="B33" s="4"/>
-      <c r="C33" s="11" t="str">
+      <c r="C33" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-Y-2-SC1</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="4"/>
-      <c r="C34" s="11" t="str">
+      <c r="C34" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-Y-2-SC1-L</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>37</v>
       </c>
       <c r="B35" s="4"/>
-      <c r="C35" s="11" t="str">
+      <c r="C35" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-Y-2-SC1-R</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="4"/>
-      <c r="C36" s="11" t="str">
+      <c r="C36" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-Y-3-SC1</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="4"/>
-      <c r="C37" s="11" t="str">
+      <c r="C37" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-Y-3-SC1-L</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="4"/>
-      <c r="C38" s="11" t="str">
+      <c r="C38" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-Y-3-SC1-R</v>
       </c>
@@ -1593,9 +1593,9 @@
         <v>35</v>
       </c>
       <c r="B39" s="4"/>
-      <c r="C39" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>King-Y-2-SC1</v>
+      <c r="C39" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>King-Y-3-SC2</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>0</v>
@@ -1604,10 +1604,10 @@
         <v>3</v>
       </c>
       <c r="F39" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H39" s="4"/>
     </row>
@@ -1616,7 +1616,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="4"/>
-      <c r="C40" s="11" t="str">
+      <c r="C40" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-Y-3-SC2-L</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="4"/>
-      <c r="C41" s="11" t="str">
+      <c r="C41" s="8" t="str">
         <f t="shared" si="0"/>
         <v>King-Y-3-SC2-R</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="7"/>
-      <c r="C42" s="13" t="str">
+      <c r="C42" s="10" t="str">
         <f t="shared" si="0"/>
         <v>King-Y-4-T</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>67</v>
       </c>
       <c r="B43" s="6"/>
-      <c r="C43" s="12" t="str">
+      <c r="C43" s="9" t="str">
         <f t="shared" si="0"/>
         <v>Balt</v>
       </c>
@@ -1708,7 +1708,7 @@
       <c r="B44" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="11" t="str">
+      <c r="C44" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC1</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>36</v>
       </c>
       <c r="B45" s="4"/>
-      <c r="C45" s="11" t="str">
+      <c r="C45" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC1-L</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>37</v>
       </c>
       <c r="B46" s="4"/>
-      <c r="C46" s="11" t="str">
+      <c r="C46" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC1-R</v>
       </c>
@@ -1771,7 +1771,7 @@
       <c r="B47" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C47" s="11" t="str">
+      <c r="C47" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC2</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>36</v>
       </c>
       <c r="B48" s="4"/>
-      <c r="C48" s="11" t="str">
+      <c r="C48" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC2-L</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>37</v>
       </c>
       <c r="B49" s="4"/>
-      <c r="C49" s="11" t="str">
+      <c r="C49" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC2-R</v>
       </c>
@@ -1834,7 +1834,7 @@
       <c r="B50" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="11" t="str">
+      <c r="C50" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC3</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>36</v>
       </c>
       <c r="B51" s="4"/>
-      <c r="C51" s="11" t="str">
+      <c r="C51" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC3-L</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>37</v>
       </c>
       <c r="B52" s="4"/>
-      <c r="C52" s="11" t="str">
+      <c r="C52" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC3-R</v>
       </c>
@@ -1897,7 +1897,7 @@
       <c r="B53" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="11" t="str">
+      <c r="C53" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC4</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>36</v>
       </c>
       <c r="B54" s="4"/>
-      <c r="C54" s="11" t="str">
+      <c r="C54" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC4-L</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>37</v>
       </c>
       <c r="B55" s="4"/>
-      <c r="C55" s="11" t="str">
+      <c r="C55" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC4-R</v>
       </c>
@@ -1960,7 +1960,7 @@
       <c r="B56" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C56" s="11" t="str">
+      <c r="C56" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC5</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>36</v>
       </c>
       <c r="B57" s="4"/>
-      <c r="C57" s="11" t="str">
+      <c r="C57" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC5-L</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>37</v>
       </c>
       <c r="B58" s="4"/>
-      <c r="C58" s="11" t="str">
+      <c r="C58" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC5-R</v>
       </c>
@@ -2023,7 +2023,7 @@
       <c r="B59" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C59" s="11" t="str">
+      <c r="C59" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC6</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>36</v>
       </c>
       <c r="B60" s="4"/>
-      <c r="C60" s="11" t="str">
+      <c r="C60" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC6-L</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>37</v>
       </c>
       <c r="B61" s="4"/>
-      <c r="C61" s="11" t="str">
+      <c r="C61" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC6-R</v>
       </c>
@@ -2086,7 +2086,7 @@
       <c r="B62" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="11" t="str">
+      <c r="C62" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC7</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>36</v>
       </c>
       <c r="B63" s="4"/>
-      <c r="C63" s="11" t="str">
+      <c r="C63" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC7-L</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>37</v>
       </c>
       <c r="B64" s="4"/>
-      <c r="C64" s="11" t="str">
+      <c r="C64" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-SC7-R</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>68</v>
       </c>
       <c r="B65" s="4"/>
-      <c r="C65" s="11" t="str">
+      <c r="C65" s="8" t="str">
         <f t="shared" si="0"/>
         <v>Balt-Y</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>50</v>
       </c>
       <c r="B66" s="4"/>
-      <c r="C66" s="11" t="str">
+      <c r="C66" s="8" t="str">
         <f t="shared" ref="C66:C69" si="1">_xlfn.TEXTJOIN("-", TRUE, _xlfn.UNIQUE(D66:H66))</f>
         <v>Balt-Y-1</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>51</v>
       </c>
       <c r="B67" s="4"/>
-      <c r="C67" s="11" t="str">
+      <c r="C67" s="8" t="str">
         <f t="shared" si="1"/>
         <v>Balt-Y-2</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>52</v>
       </c>
       <c r="B68" s="4"/>
-      <c r="C68" s="11" t="str">
+      <c r="C68" s="8" t="str">
         <f t="shared" si="1"/>
         <v>Balt-Y-3</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>53</v>
       </c>
       <c r="B69" s="7"/>
-      <c r="C69" s="13" t="str">
+      <c r="C69" s="10" t="str">
         <f t="shared" si="1"/>
         <v>Balt-Y-4</v>
       </c>
@@ -2252,7 +2252,7 @@
       <c r="B70" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C70" s="14" t="str">
+      <c r="C70" s="11" t="str">
         <f>_xlfn.TEXTJOIN("-", TRUE, _xlfn.UNIQUE(D70:H70))</f>
         <v>Balt-Y-Q</v>
       </c>
@@ -2271,7 +2271,7 @@
       <c r="B71" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C71" s="11" t="str">
+      <c r="C71" s="8" t="str">
         <f>_xlfn.TEXTJOIN("-", TRUE, _xlfn.UNIQUE(D71:H71))</f>
         <v>King-Y-Q</v>
       </c>
